--- a/digi-finance/data/digi-fin-data.xlsx
+++ b/digi-finance/data/digi-fin-data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AER\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\viser\OneDrive\Dokumen\Github repository\data-consultation-2026\digi-finance\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B6B104F-4805-4104-80D9-FE5187CE4250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9145A945-28D2-4B80-8D74-4CA48DAA18A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Responses" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6098" uniqueCount="586">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6134" uniqueCount="590">
   <si>
     <t>Name (Optional)</t>
   </si>
@@ -1802,6 +1802,18 @@
   <si>
     <t>Financial Anxiety</t>
   </si>
+  <si>
+    <t>Higher Order Factor</t>
+  </si>
+  <si>
+    <t>Digital financial literacy</t>
+  </si>
+  <si>
+    <t>Financial literacy</t>
+  </si>
+  <si>
+    <t>Financial well-being</t>
+  </si>
 </sst>
 </file>
 
@@ -2199,10 +2211,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:BC371">
   <tableColumns count="55">
@@ -2468,32 +2476,32 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:BD371"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.88671875" style="4" customWidth="1"/>
-    <col min="2" max="2" width="18.88671875" customWidth="1"/>
-    <col min="3" max="3" width="18.88671875" style="4" customWidth="1"/>
-    <col min="4" max="4" width="30.33203125" customWidth="1"/>
-    <col min="5" max="5" width="18.88671875" style="4" customWidth="1"/>
-    <col min="6" max="6" width="25.21875" customWidth="1"/>
-    <col min="7" max="7" width="31.33203125" customWidth="1"/>
-    <col min="8" max="8" width="18.88671875" customWidth="1"/>
-    <col min="9" max="9" width="37.6640625" style="4" customWidth="1"/>
-    <col min="10" max="17" width="37.6640625" customWidth="1"/>
-    <col min="18" max="19" width="37.6640625" style="4" customWidth="1"/>
+    <col min="1" max="1" width="18.85546875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" customWidth="1"/>
+    <col min="3" max="3" width="18.85546875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="30.28515625" customWidth="1"/>
+    <col min="5" max="5" width="18.85546875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="25.28515625" customWidth="1"/>
+    <col min="7" max="7" width="31.28515625" customWidth="1"/>
+    <col min="8" max="8" width="18.85546875" customWidth="1"/>
+    <col min="9" max="9" width="37.7109375" style="4" customWidth="1"/>
+    <col min="10" max="17" width="37.7109375" customWidth="1"/>
+    <col min="18" max="19" width="37.7109375" style="4" customWidth="1"/>
     <col min="20" max="20" width="27" style="4" customWidth="1"/>
-    <col min="21" max="21" width="36.77734375" style="4" customWidth="1"/>
-    <col min="22" max="25" width="37.6640625" style="4" customWidth="1"/>
-    <col min="26" max="26" width="35.33203125" style="4" customWidth="1"/>
-    <col min="27" max="27" width="20.33203125" style="4" customWidth="1"/>
-    <col min="28" max="28" width="35.109375" style="4" customWidth="1"/>
-    <col min="29" max="44" width="37.6640625" style="4" customWidth="1"/>
-    <col min="45" max="45" width="23.21875" style="4" customWidth="1"/>
-    <col min="46" max="55" width="37.6640625" style="4" customWidth="1"/>
-    <col min="56" max="61" width="18.88671875" customWidth="1"/>
+    <col min="21" max="21" width="36.7109375" style="4" customWidth="1"/>
+    <col min="22" max="25" width="37.7109375" style="4" customWidth="1"/>
+    <col min="26" max="26" width="35.28515625" style="4" customWidth="1"/>
+    <col min="27" max="27" width="20.28515625" style="4" customWidth="1"/>
+    <col min="28" max="28" width="35.140625" style="4" customWidth="1"/>
+    <col min="29" max="44" width="37.7109375" style="4" customWidth="1"/>
+    <col min="45" max="45" width="23.28515625" style="4" customWidth="1"/>
+    <col min="46" max="55" width="37.7109375" style="4" customWidth="1"/>
+    <col min="56" max="61" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2660,7 +2668,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="2" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>165</v>
       </c>
@@ -2827,7 +2835,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>166</v>
       </c>
@@ -2994,7 +3002,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>167</v>
       </c>
@@ -3161,7 +3169,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>168</v>
       </c>
@@ -3328,7 +3336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>169</v>
       </c>
@@ -3495,7 +3503,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>170</v>
       </c>
@@ -3662,7 +3670,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>171</v>
       </c>
@@ -3829,7 +3837,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>172</v>
       </c>
@@ -3996,7 +4004,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>173</v>
       </c>
@@ -4163,7 +4171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>174</v>
       </c>
@@ -4330,7 +4338,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>175</v>
       </c>
@@ -4497,7 +4505,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>176</v>
       </c>
@@ -4664,7 +4672,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>177</v>
       </c>
@@ -4831,7 +4839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>178</v>
       </c>
@@ -4998,7 +5006,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>179</v>
       </c>
@@ -5165,7 +5173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>180</v>
       </c>
@@ -5332,7 +5340,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>181</v>
       </c>
@@ -5499,7 +5507,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>182</v>
       </c>
@@ -5666,7 +5674,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>183</v>
       </c>
@@ -5833,7 +5841,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>184</v>
       </c>
@@ -6000,7 +6008,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>185</v>
       </c>
@@ -6167,7 +6175,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>186</v>
       </c>
@@ -6334,7 +6342,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>187</v>
       </c>
@@ -6501,7 +6509,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>188</v>
       </c>
@@ -6668,7 +6676,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>189</v>
       </c>
@@ -6835,7 +6843,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>190</v>
       </c>
@@ -7002,7 +7010,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>191</v>
       </c>
@@ -7169,7 +7177,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>192</v>
       </c>
@@ -7336,7 +7344,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>193</v>
       </c>
@@ -7503,7 +7511,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>194</v>
       </c>
@@ -7670,7 +7678,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>195</v>
       </c>
@@ -7837,7 +7845,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>196</v>
       </c>
@@ -8004,7 +8012,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
         <v>197</v>
       </c>
@@ -8171,7 +8179,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>198</v>
       </c>
@@ -8338,7 +8346,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
         <v>199</v>
       </c>
@@ -8505,7 +8513,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
         <v>200</v>
       </c>
@@ -8672,7 +8680,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
         <v>201</v>
       </c>
@@ -8839,7 +8847,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>202</v>
       </c>
@@ -9006,7 +9014,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
         <v>203</v>
       </c>
@@ -9173,7 +9181,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
         <v>204</v>
       </c>
@@ -9340,7 +9348,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
         <v>205</v>
       </c>
@@ -9507,7 +9515,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
         <v>206</v>
       </c>
@@ -9674,7 +9682,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
         <v>207</v>
       </c>
@@ -9841,7 +9849,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
         <v>208</v>
       </c>
@@ -10008,7 +10016,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
         <v>209</v>
       </c>
@@ -10175,7 +10183,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
         <v>210</v>
       </c>
@@ -10342,7 +10350,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
         <v>211</v>
       </c>
@@ -10509,7 +10517,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
         <v>212</v>
       </c>
@@ -10676,7 +10684,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
         <v>213</v>
       </c>
@@ -10843,7 +10851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
         <v>214</v>
       </c>
@@ -11010,7 +11018,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
         <v>215</v>
       </c>
@@ -11177,7 +11185,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
         <v>216</v>
       </c>
@@ -11344,7 +11352,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
         <v>217</v>
       </c>
@@ -11511,7 +11519,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
         <v>218</v>
       </c>
@@ -11678,7 +11686,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
         <v>219</v>
       </c>
@@ -11845,7 +11853,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
         <v>220</v>
       </c>
@@ -12012,7 +12020,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
         <v>221</v>
       </c>
@@ -12179,7 +12187,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
         <v>222</v>
       </c>
@@ -12346,7 +12354,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
         <v>223</v>
       </c>
@@ -12513,7 +12521,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
         <v>224</v>
       </c>
@@ -12680,7 +12688,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
         <v>225</v>
       </c>
@@ -12847,7 +12855,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
         <v>226</v>
       </c>
@@ -13014,7 +13022,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
         <v>227</v>
       </c>
@@ -13181,7 +13189,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
         <v>228</v>
       </c>
@@ -13348,7 +13356,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
         <v>229</v>
       </c>
@@ -13515,7 +13523,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
         <v>230</v>
       </c>
@@ -13682,7 +13690,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="68" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
         <v>231</v>
       </c>
@@ -13849,7 +13857,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
         <v>232</v>
       </c>
@@ -14016,7 +14024,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
         <v>233</v>
       </c>
@@ -14183,7 +14191,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
         <v>234</v>
       </c>
@@ -14350,7 +14358,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
         <v>235</v>
       </c>
@@ -14517,7 +14525,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
         <v>236</v>
       </c>
@@ -14684,7 +14692,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
         <v>237</v>
       </c>
@@ -14851,7 +14859,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
         <v>238</v>
       </c>
@@ -15018,7 +15026,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
         <v>239</v>
       </c>
@@ -15185,7 +15193,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="77" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
         <v>240</v>
       </c>
@@ -15352,7 +15360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
         <v>241</v>
       </c>
@@ -15519,7 +15527,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="3" t="s">
         <v>242</v>
       </c>
@@ -15686,7 +15694,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="s">
         <v>243</v>
       </c>
@@ -15853,7 +15861,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
         <v>244</v>
       </c>
@@ -16020,7 +16028,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
         <v>245</v>
       </c>
@@ -16187,7 +16195,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="3" t="s">
         <v>246</v>
       </c>
@@ -16354,7 +16362,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="3" t="s">
         <v>247</v>
       </c>
@@ -16521,7 +16529,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="85" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="3" t="s">
         <v>248</v>
       </c>
@@ -16688,7 +16696,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="3" t="s">
         <v>249</v>
       </c>
@@ -16855,7 +16863,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="s">
         <v>250</v>
       </c>
@@ -17022,7 +17030,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
         <v>251</v>
       </c>
@@ -17189,7 +17197,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="3" t="s">
         <v>252</v>
       </c>
@@ -17356,7 +17364,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
         <v>253</v>
       </c>
@@ -17523,7 +17531,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
         <v>254</v>
       </c>
@@ -17690,7 +17698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="3" t="s">
         <v>255</v>
       </c>
@@ -17857,7 +17865,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="93" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="s">
         <v>256</v>
       </c>
@@ -18024,7 +18032,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="3" t="s">
         <v>257</v>
       </c>
@@ -18191,7 +18199,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="3" t="s">
         <v>258</v>
       </c>
@@ -18358,7 +18366,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="3" t="s">
         <v>259</v>
       </c>
@@ -18525,7 +18533,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="97" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
         <v>260</v>
       </c>
@@ -18692,7 +18700,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="98" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="3" t="s">
         <v>261</v>
       </c>
@@ -18859,7 +18867,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="99" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
         <v>262</v>
       </c>
@@ -19026,7 +19034,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="100" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
         <v>263</v>
       </c>
@@ -19193,7 +19201,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="3" t="s">
         <v>264</v>
       </c>
@@ -19360,7 +19368,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="3" t="s">
         <v>265</v>
       </c>
@@ -19527,7 +19535,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="3" t="s">
         <v>266</v>
       </c>
@@ -19694,7 +19702,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="104" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="3" t="s">
         <v>267</v>
       </c>
@@ -19861,7 +19869,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
         <v>268</v>
       </c>
@@ -20028,7 +20036,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="106" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="3" t="s">
         <v>269</v>
       </c>
@@ -20195,7 +20203,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="107" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
         <v>270</v>
       </c>
@@ -20362,7 +20370,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="s">
         <v>271</v>
       </c>
@@ -20529,7 +20537,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="109" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="3" t="s">
         <v>272</v>
       </c>
@@ -20696,7 +20704,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="110" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="3" t="s">
         <v>273</v>
       </c>
@@ -20863,7 +20871,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="111" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="3" t="s">
         <v>274</v>
       </c>
@@ -21030,7 +21038,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="112" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="3" t="s">
         <v>275</v>
       </c>
@@ -21197,7 +21205,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="113" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="3" t="s">
         <v>276</v>
       </c>
@@ -21364,7 +21372,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="114" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="3" t="s">
         <v>277</v>
       </c>
@@ -21531,7 +21539,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="115" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="s">
         <v>278</v>
       </c>
@@ -21698,7 +21706,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="116" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
         <v>279</v>
       </c>
@@ -21865,7 +21873,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="117" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="3" t="s">
         <v>280</v>
       </c>
@@ -22032,7 +22040,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="3" t="s">
         <v>281</v>
       </c>
@@ -22199,7 +22207,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
         <v>282</v>
       </c>
@@ -22366,7 +22374,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="120" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
         <v>283</v>
       </c>
@@ -22533,7 +22541,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="121" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="3" t="s">
         <v>284</v>
       </c>
@@ -22700,7 +22708,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="122" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="3" t="s">
         <v>285</v>
       </c>
@@ -22867,7 +22875,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="123" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="3" t="s">
         <v>286</v>
       </c>
@@ -23034,7 +23042,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="124" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="3" t="s">
         <v>287</v>
       </c>
@@ -23201,7 +23209,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="125" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="3" t="s">
         <v>288</v>
       </c>
@@ -23368,7 +23376,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="3" t="s">
         <v>289</v>
       </c>
@@ -23535,7 +23543,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="127" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="3" t="s">
         <v>290</v>
       </c>
@@ -23702,7 +23710,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="3" t="s">
         <v>291</v>
       </c>
@@ -23869,7 +23877,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="129" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="3" t="s">
         <v>292</v>
       </c>
@@ -24036,7 +24044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="3" t="s">
         <v>293</v>
       </c>
@@ -24203,7 +24211,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="131" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="3" t="s">
         <v>294</v>
       </c>
@@ -24370,7 +24378,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="3" t="s">
         <v>295</v>
       </c>
@@ -24537,7 +24545,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="133" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="3" t="s">
         <v>296</v>
       </c>
@@ -24704,7 +24712,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="134" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="3" t="s">
         <v>297</v>
       </c>
@@ -24871,7 +24879,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="135" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="3" t="s">
         <v>298</v>
       </c>
@@ -25038,7 +25046,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="136" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="3" t="s">
         <v>299</v>
       </c>
@@ -25205,7 +25213,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="137" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="3" t="s">
         <v>300</v>
       </c>
@@ -25372,7 +25380,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="138" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="3" t="s">
         <v>301</v>
       </c>
@@ -25539,7 +25547,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="139" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="3" t="s">
         <v>302</v>
       </c>
@@ -25706,7 +25714,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="140" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="3" t="s">
         <v>303</v>
       </c>
@@ -25873,7 +25881,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="141" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="3" t="s">
         <v>304</v>
       </c>
@@ -26040,7 +26048,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="142" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="3" t="s">
         <v>305</v>
       </c>
@@ -26207,7 +26215,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="143" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="3" t="s">
         <v>306</v>
       </c>
@@ -26374,7 +26382,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="144" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="3" t="s">
         <v>307</v>
       </c>
@@ -26541,7 +26549,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="145" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="3" t="s">
         <v>308</v>
       </c>
@@ -26708,7 +26716,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="146" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="3" t="s">
         <v>309</v>
       </c>
@@ -26875,7 +26883,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="147" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="3" t="s">
         <v>310</v>
       </c>
@@ -27042,7 +27050,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="148" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="3" t="s">
         <v>311</v>
       </c>
@@ -27209,7 +27217,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="149" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="3" t="s">
         <v>312</v>
       </c>
@@ -27376,7 +27384,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="150" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="3" t="s">
         <v>313</v>
       </c>
@@ -27543,7 +27551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="3" t="s">
         <v>314</v>
       </c>
@@ -27710,7 +27718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="3" t="s">
         <v>315</v>
       </c>
@@ -27877,7 +27885,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="153" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="3" t="s">
         <v>316</v>
       </c>
@@ -28044,7 +28052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="3" t="s">
         <v>317</v>
       </c>
@@ -28211,7 +28219,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="155" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="3" t="s">
         <v>318</v>
       </c>
@@ -28378,7 +28386,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="156" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="3" t="s">
         <v>319</v>
       </c>
@@ -28545,7 +28553,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="157" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="3" t="s">
         <v>320</v>
       </c>
@@ -28712,7 +28720,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="158" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="3" t="s">
         <v>321</v>
       </c>
@@ -28879,7 +28887,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="159" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="3" t="s">
         <v>322</v>
       </c>
@@ -29046,7 +29054,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="160" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="3" t="s">
         <v>323</v>
       </c>
@@ -29213,7 +29221,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="3" t="s">
         <v>324</v>
       </c>
@@ -29380,7 +29388,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="162" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="3" t="s">
         <v>325</v>
       </c>
@@ -29547,7 +29555,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="163" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="3" t="s">
         <v>326</v>
       </c>
@@ -29714,7 +29722,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="3" t="s">
         <v>327</v>
       </c>
@@ -29881,7 +29889,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="165" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="3" t="s">
         <v>328</v>
       </c>
@@ -30048,7 +30056,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="166" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="3" t="s">
         <v>329</v>
       </c>
@@ -30215,7 +30223,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="167" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="3" t="s">
         <v>330</v>
       </c>
@@ -30382,7 +30390,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="168" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="3" t="s">
         <v>331</v>
       </c>
@@ -30549,7 +30557,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="169" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="3" t="s">
         <v>332</v>
       </c>
@@ -30716,7 +30724,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="170" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="3" t="s">
         <v>333</v>
       </c>
@@ -30883,7 +30891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="3" t="s">
         <v>334</v>
       </c>
@@ -31050,7 +31058,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="172" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="3" t="s">
         <v>335</v>
       </c>
@@ -31217,7 +31225,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="173" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="3" t="s">
         <v>336</v>
       </c>
@@ -31384,7 +31392,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="174" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="3" t="s">
         <v>337</v>
       </c>
@@ -31551,7 +31559,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="175" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="3" t="s">
         <v>338</v>
       </c>
@@ -31718,7 +31726,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="176" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="3" t="s">
         <v>339</v>
       </c>
@@ -31885,7 +31893,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="177" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="3" t="s">
         <v>340</v>
       </c>
@@ -32052,7 +32060,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="178" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="3" t="s">
         <v>341</v>
       </c>
@@ -32219,7 +32227,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="179" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="3" t="s">
         <v>342</v>
       </c>
@@ -32386,7 +32394,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="180" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="3" t="s">
         <v>343</v>
       </c>
@@ -32553,7 +32561,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="181" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="3" t="s">
         <v>344</v>
       </c>
@@ -32720,7 +32728,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="182" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="3" t="s">
         <v>345</v>
       </c>
@@ -32887,7 +32895,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="183" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="3" t="s">
         <v>346</v>
       </c>
@@ -33054,7 +33062,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="184" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="3" t="s">
         <v>347</v>
       </c>
@@ -33221,7 +33229,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="185" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="3" t="s">
         <v>348</v>
       </c>
@@ -33388,7 +33396,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="186" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="3" t="s">
         <v>349</v>
       </c>
@@ -33555,7 +33563,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="187" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="3" t="s">
         <v>350</v>
       </c>
@@ -33722,7 +33730,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="188" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="3" t="s">
         <v>351</v>
       </c>
@@ -33889,7 +33897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="3" t="s">
         <v>352</v>
       </c>
@@ -34056,7 +34064,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="190" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="3" t="s">
         <v>353</v>
       </c>
@@ -34223,7 +34231,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="191" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="3" t="s">
         <v>354</v>
       </c>
@@ -34390,7 +34398,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="192" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="3" t="s">
         <v>355</v>
       </c>
@@ -34557,7 +34565,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="193" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="3" t="s">
         <v>356</v>
       </c>
@@ -34724,7 +34732,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="194" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="3" t="s">
         <v>357</v>
       </c>
@@ -34891,7 +34899,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="195" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="3" t="s">
         <v>358</v>
       </c>
@@ -35058,7 +35066,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="196" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="3" t="s">
         <v>359</v>
       </c>
@@ -35225,7 +35233,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="197" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="3" t="s">
         <v>360</v>
       </c>
@@ -35392,7 +35400,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="198" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="3" t="s">
         <v>361</v>
       </c>
@@ -35559,7 +35567,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="199" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="3" t="s">
         <v>362</v>
       </c>
@@ -35726,7 +35734,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="200" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="3" t="s">
         <v>363</v>
       </c>
@@ -35893,7 +35901,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="201" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="3" t="s">
         <v>364</v>
       </c>
@@ -36060,7 +36068,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="202" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="3" t="s">
         <v>365</v>
       </c>
@@ -36227,7 +36235,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="203" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="3" t="s">
         <v>366</v>
       </c>
@@ -36394,7 +36402,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="204" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="3" t="s">
         <v>367</v>
       </c>
@@ -36561,7 +36569,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="205" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="3" t="s">
         <v>368</v>
       </c>
@@ -36728,7 +36736,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="206" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="3" t="s">
         <v>369</v>
       </c>
@@ -36895,7 +36903,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="207" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="3" t="s">
         <v>370</v>
       </c>
@@ -37062,7 +37070,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="208" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="3" t="s">
         <v>371</v>
       </c>
@@ -37229,7 +37237,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="209" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="3" t="s">
         <v>372</v>
       </c>
@@ -37396,7 +37404,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="210" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="3" t="s">
         <v>373</v>
       </c>
@@ -37563,7 +37571,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="211" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="3" t="s">
         <v>374</v>
       </c>
@@ -37730,7 +37738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="3" t="s">
         <v>375</v>
       </c>
@@ -37897,7 +37905,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="213" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="3" t="s">
         <v>376</v>
       </c>
@@ -38064,7 +38072,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="214" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="3" t="s">
         <v>377</v>
       </c>
@@ -38231,7 +38239,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="215" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="3" t="s">
         <v>378</v>
       </c>
@@ -38398,7 +38406,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="216" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="3" t="s">
         <v>379</v>
       </c>
@@ -38565,7 +38573,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="217" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="3" t="s">
         <v>380</v>
       </c>
@@ -38732,7 +38740,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="218" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="3" t="s">
         <v>381</v>
       </c>
@@ -38899,7 +38907,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="219" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="3" t="s">
         <v>382</v>
       </c>
@@ -39066,7 +39074,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="220" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="3" t="s">
         <v>383</v>
       </c>
@@ -39233,7 +39241,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="221" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="3" t="s">
         <v>384</v>
       </c>
@@ -39400,7 +39408,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="222" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="3" t="s">
         <v>385</v>
       </c>
@@ -39567,7 +39575,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="223" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="3" t="s">
         <v>386</v>
       </c>
@@ -39734,7 +39742,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="224" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="3" t="s">
         <v>387</v>
       </c>
@@ -39901,7 +39909,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="225" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="3" t="s">
         <v>388</v>
       </c>
@@ -40068,7 +40076,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="226" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="3" t="s">
         <v>389</v>
       </c>
@@ -40235,7 +40243,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="227" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="3" t="s">
         <v>390</v>
       </c>
@@ -40402,7 +40410,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="228" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="3" t="s">
         <v>391</v>
       </c>
@@ -40569,7 +40577,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="229" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="3" t="s">
         <v>392</v>
       </c>
@@ -40736,7 +40744,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="230" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="3" t="s">
         <v>393</v>
       </c>
@@ -40903,7 +40911,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="231" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="3" t="s">
         <v>394</v>
       </c>
@@ -41070,7 +41078,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="232" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="3" t="s">
         <v>395</v>
       </c>
@@ -41237,7 +41245,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="233" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="3" t="s">
         <v>396</v>
       </c>
@@ -41404,7 +41412,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="234" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="3" t="s">
         <v>397</v>
       </c>
@@ -41571,7 +41579,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="235" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="3" t="s">
         <v>398</v>
       </c>
@@ -41738,7 +41746,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="236" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="3" t="s">
         <v>399</v>
       </c>
@@ -41905,7 +41913,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="237" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="3" t="s">
         <v>400</v>
       </c>
@@ -42072,7 +42080,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="238" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="3" t="s">
         <v>401</v>
       </c>
@@ -42239,7 +42247,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="239" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="3" t="s">
         <v>402</v>
       </c>
@@ -42406,7 +42414,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="240" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="3" t="s">
         <v>403</v>
       </c>
@@ -42573,7 +42581,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="241" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="3" t="s">
         <v>404</v>
       </c>
@@ -42740,7 +42748,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="242" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="3" t="s">
         <v>405</v>
       </c>
@@ -42907,7 +42915,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="243" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="3" t="s">
         <v>406</v>
       </c>
@@ -43074,7 +43082,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="244" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="3" t="s">
         <v>407</v>
       </c>
@@ -43241,7 +43249,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="245" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="3" t="s">
         <v>408</v>
       </c>
@@ -43408,7 +43416,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="246" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="3" t="s">
         <v>409</v>
       </c>
@@ -43575,7 +43583,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="247" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="3" t="s">
         <v>410</v>
       </c>
@@ -43742,7 +43750,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="248" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="3" t="s">
         <v>411</v>
       </c>
@@ -43909,7 +43917,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="249" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="3" t="s">
         <v>412</v>
       </c>
@@ -44076,7 +44084,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="250" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="3" t="s">
         <v>413</v>
       </c>
@@ -44243,7 +44251,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="251" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="3" t="s">
         <v>414</v>
       </c>
@@ -44410,7 +44418,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="252" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="3" t="s">
         <v>415</v>
       </c>
@@ -44577,7 +44585,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="253" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="3" t="s">
         <v>416</v>
       </c>
@@ -44744,7 +44752,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="254" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="3" t="s">
         <v>417</v>
       </c>
@@ -44911,7 +44919,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="255" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="3" t="s">
         <v>418</v>
       </c>
@@ -45078,7 +45086,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="256" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="3" t="s">
         <v>419</v>
       </c>
@@ -45245,7 +45253,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="257" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="3" t="s">
         <v>420</v>
       </c>
@@ -45412,7 +45420,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="258" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="3" t="s">
         <v>421</v>
       </c>
@@ -45579,7 +45587,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="259" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="3" t="s">
         <v>422</v>
       </c>
@@ -45746,7 +45754,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="260" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="3" t="s">
         <v>423</v>
       </c>
@@ -45913,7 +45921,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="261" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="3" t="s">
         <v>424</v>
       </c>
@@ -46080,7 +46088,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="262" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="3" t="s">
         <v>425</v>
       </c>
@@ -46247,7 +46255,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="263" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="3" t="s">
         <v>426</v>
       </c>
@@ -46414,7 +46422,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="264" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="3" t="s">
         <v>427</v>
       </c>
@@ -46581,7 +46589,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="265" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="3" t="s">
         <v>428</v>
       </c>
@@ -46748,7 +46756,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="266" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="3" t="s">
         <v>429</v>
       </c>
@@ -46915,7 +46923,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="267" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="3" t="s">
         <v>430</v>
       </c>
@@ -47082,7 +47090,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="268" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="3" t="s">
         <v>431</v>
       </c>
@@ -47249,7 +47257,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="269" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="3" t="s">
         <v>432</v>
       </c>
@@ -47416,7 +47424,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="270" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="3" t="s">
         <v>433</v>
       </c>
@@ -47583,7 +47591,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="271" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="3" t="s">
         <v>434</v>
       </c>
@@ -47750,7 +47758,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="272" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="3" t="s">
         <v>435</v>
       </c>
@@ -47917,7 +47925,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="273" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="3" t="s">
         <v>436</v>
       </c>
@@ -48084,7 +48092,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="274" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="3" t="s">
         <v>437</v>
       </c>
@@ -48251,7 +48259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="3" t="s">
         <v>438</v>
       </c>
@@ -48418,7 +48426,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="276" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="3" t="s">
         <v>439</v>
       </c>
@@ -48585,7 +48593,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="277" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="3" t="s">
         <v>440</v>
       </c>
@@ -48752,7 +48760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="3" t="s">
         <v>441</v>
       </c>
@@ -48919,7 +48927,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="3" t="s">
         <v>442</v>
       </c>
@@ -49086,7 +49094,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="280" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="3" t="s">
         <v>443</v>
       </c>
@@ -49253,7 +49261,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="281" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="3" t="s">
         <v>444</v>
       </c>
@@ -49420,7 +49428,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="282" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="3" t="s">
         <v>445</v>
       </c>
@@ -49587,7 +49595,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="283" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="3" t="s">
         <v>446</v>
       </c>
@@ -49754,7 +49762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="284" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="3" t="s">
         <v>447</v>
       </c>
@@ -49921,7 +49929,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="285" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="3" t="s">
         <v>448</v>
       </c>
@@ -50088,7 +50096,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="286" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="3" t="s">
         <v>449</v>
       </c>
@@ -50255,7 +50263,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="287" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="3" t="s">
         <v>450</v>
       </c>
@@ -50422,7 +50430,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="288" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="3" t="s">
         <v>451</v>
       </c>
@@ -50589,7 +50597,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="289" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="3" t="s">
         <v>452</v>
       </c>
@@ -50756,7 +50764,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="290" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="3" t="s">
         <v>453</v>
       </c>
@@ -50923,7 +50931,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="291" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="3" t="s">
         <v>454</v>
       </c>
@@ -51090,7 +51098,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="292" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="3" t="s">
         <v>455</v>
       </c>
@@ -51257,7 +51265,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="293" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="3" t="s">
         <v>456</v>
       </c>
@@ -51424,7 +51432,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="294" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="3" t="s">
         <v>457</v>
       </c>
@@ -51591,7 +51599,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="295" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="3" t="s">
         <v>458</v>
       </c>
@@ -51758,7 +51766,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="296" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="3" t="s">
         <v>459</v>
       </c>
@@ -51925,7 +51933,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="297" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="3" t="s">
         <v>460</v>
       </c>
@@ -52092,7 +52100,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="298" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" s="3" t="s">
         <v>461</v>
       </c>
@@ -52259,7 +52267,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="299" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" s="3" t="s">
         <v>462</v>
       </c>
@@ -52426,7 +52434,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="300" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A300" s="3" t="s">
         <v>463</v>
       </c>
@@ -52593,7 +52601,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="301" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A301" s="3" t="s">
         <v>464</v>
       </c>
@@ -52760,7 +52768,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="302" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A302" s="3" t="s">
         <v>465</v>
       </c>
@@ -52927,7 +52935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="303" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="3" t="s">
         <v>466</v>
       </c>
@@ -53094,7 +53102,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="304" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A304" s="3" t="s">
         <v>467</v>
       </c>
@@ -53261,7 +53269,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="305" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A305" s="3" t="s">
         <v>468</v>
       </c>
@@ -53428,7 +53436,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="306" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A306" s="3" t="s">
         <v>469</v>
       </c>
@@ -53595,7 +53603,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="307" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A307" s="3" t="s">
         <v>470</v>
       </c>
@@ -53762,7 +53770,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="308" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A308" s="3" t="s">
         <v>471</v>
       </c>
@@ -53929,7 +53937,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="309" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A309" s="3" t="s">
         <v>472</v>
       </c>
@@ -54096,7 +54104,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="310" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A310" s="3" t="s">
         <v>473</v>
       </c>
@@ -54263,7 +54271,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="311" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A311" s="3" t="s">
         <v>474</v>
       </c>
@@ -54430,7 +54438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="312" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A312" s="3" t="s">
         <v>475</v>
       </c>
@@ -54597,7 +54605,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="313" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A313" s="3" t="s">
         <v>476</v>
       </c>
@@ -54764,7 +54772,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="314" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A314" s="3" t="s">
         <v>477</v>
       </c>
@@ -54931,7 +54939,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="315" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A315" s="3" t="s">
         <v>478</v>
       </c>
@@ -55098,7 +55106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="316" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A316" s="3" t="s">
         <v>479</v>
       </c>
@@ -55265,7 +55273,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="317" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A317" s="3" t="s">
         <v>480</v>
       </c>
@@ -55432,7 +55440,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="318" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A318" s="3" t="s">
         <v>481</v>
       </c>
@@ -55599,7 +55607,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="319" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A319" s="3" t="s">
         <v>482</v>
       </c>
@@ -55766,7 +55774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="320" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A320" s="3" t="s">
         <v>483</v>
       </c>
@@ -55933,7 +55941,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="321" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A321" s="3" t="s">
         <v>484</v>
       </c>
@@ -56100,7 +56108,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="322" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A322" s="3" t="s">
         <v>485</v>
       </c>
@@ -56267,7 +56275,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="323" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A323" s="3" t="s">
         <v>486</v>
       </c>
@@ -56434,7 +56442,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="324" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A324" s="3" t="s">
         <v>487</v>
       </c>
@@ -56601,7 +56609,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="325" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A325" s="3" t="s">
         <v>488</v>
       </c>
@@ -56768,7 +56776,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="326" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A326" s="3" t="s">
         <v>489</v>
       </c>
@@ -56935,7 +56943,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="327" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A327" s="3" t="s">
         <v>490</v>
       </c>
@@ -57102,7 +57110,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="328" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A328" s="3" t="s">
         <v>491</v>
       </c>
@@ -57269,7 +57277,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="329" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A329" s="3" t="s">
         <v>492</v>
       </c>
@@ -57436,7 +57444,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="330" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A330" s="3" t="s">
         <v>493</v>
       </c>
@@ -57603,7 +57611,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="331" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A331" s="3" t="s">
         <v>494</v>
       </c>
@@ -57770,7 +57778,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="332" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A332" s="3" t="s">
         <v>495</v>
       </c>
@@ -57937,7 +57945,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="333" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A333" s="3" t="s">
         <v>496</v>
       </c>
@@ -58104,7 +58112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="334" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A334" s="3" t="s">
         <v>497</v>
       </c>
@@ -58271,7 +58279,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="335" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A335" s="3" t="s">
         <v>498</v>
       </c>
@@ -58438,7 +58446,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="336" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A336" s="3" t="s">
         <v>499</v>
       </c>
@@ -58605,7 +58613,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="337" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A337" s="3" t="s">
         <v>500</v>
       </c>
@@ -58772,7 +58780,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="338" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A338" s="3" t="s">
         <v>501</v>
       </c>
@@ -58939,7 +58947,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="339" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A339" s="3" t="s">
         <v>502</v>
       </c>
@@ -59106,7 +59114,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="340" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A340" s="3" t="s">
         <v>503</v>
       </c>
@@ -59273,7 +59281,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="341" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A341" s="3" t="s">
         <v>504</v>
       </c>
@@ -59440,7 +59448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="342" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A342" s="3" t="s">
         <v>505</v>
       </c>
@@ -59607,7 +59615,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="343" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A343" s="3" t="s">
         <v>506</v>
       </c>
@@ -59774,7 +59782,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="344" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A344" s="3" t="s">
         <v>507</v>
       </c>
@@ -59941,7 +59949,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="345" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A345" s="3" t="s">
         <v>508</v>
       </c>
@@ -60108,7 +60116,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="346" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A346" s="3" t="s">
         <v>509</v>
       </c>
@@ -60275,7 +60283,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="347" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A347" s="3" t="s">
         <v>510</v>
       </c>
@@ -60442,7 +60450,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="348" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A348" s="3" t="s">
         <v>511</v>
       </c>
@@ -60609,7 +60617,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="349" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A349" s="3" t="s">
         <v>512</v>
       </c>
@@ -60776,7 +60784,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="350" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A350" s="3" t="s">
         <v>513</v>
       </c>
@@ -60943,7 +60951,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="351" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A351" s="3" t="s">
         <v>514</v>
       </c>
@@ -61110,7 +61118,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="352" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:55" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A352" s="3" t="s">
         <v>515</v>
       </c>
@@ -61277,7 +61285,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="353" spans="1:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A353" s="3" t="s">
         <v>516</v>
       </c>
@@ -61444,7 +61452,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="354" spans="1:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A354" s="3" t="s">
         <v>517</v>
       </c>
@@ -61611,7 +61619,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="355" spans="1:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A355" s="3" t="s">
         <v>518</v>
       </c>
@@ -61778,7 +61786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="356" spans="1:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A356" s="3" t="s">
         <v>519</v>
       </c>
@@ -61945,7 +61953,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="357" spans="1:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A357" s="3" t="s">
         <v>520</v>
       </c>
@@ -62112,7 +62120,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="358" spans="1:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A358" s="3" t="s">
         <v>521</v>
       </c>
@@ -62279,7 +62287,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="359" spans="1:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A359" s="3" t="s">
         <v>522</v>
       </c>
@@ -62446,7 +62454,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="360" spans="1:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A360" s="3" t="s">
         <v>523</v>
       </c>
@@ -62613,7 +62621,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="361" spans="1:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A361" s="3" t="s">
         <v>524</v>
       </c>
@@ -62780,7 +62788,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="362" spans="1:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A362" s="3" t="s">
         <v>525</v>
       </c>
@@ -62947,7 +62955,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="363" spans="1:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A363" s="3" t="s">
         <v>526</v>
       </c>
@@ -63114,7 +63122,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="364" spans="1:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A364" s="3" t="s">
         <v>527</v>
       </c>
@@ -63281,7 +63289,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="365" spans="1:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A365" s="3" t="s">
         <v>528</v>
       </c>
@@ -63448,7 +63456,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="366" spans="1:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A366" s="3" t="s">
         <v>529</v>
       </c>
@@ -63618,7 +63626,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="367" spans="1:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A367" s="3" t="s">
         <v>530</v>
       </c>
@@ -63788,7 +63796,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="368" spans="1:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A368" s="3" t="s">
         <v>531</v>
       </c>
@@ -63958,7 +63966,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="369" spans="1:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A369" s="3" t="s">
         <v>532</v>
       </c>
@@ -64128,7 +64136,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="370" spans="1:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A370" s="3" t="s">
         <v>533</v>
       </c>
@@ -64298,7 +64306,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="371" spans="1:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A371" s="3" t="s">
         <v>534</v>
       </c>
@@ -64478,15 +64486,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D39"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="92.6640625" customWidth="1"/>
+    <col min="1" max="1" width="92.7109375" customWidth="1"/>
     <col min="2" max="2" width="16" style="16" customWidth="1"/>
-    <col min="3" max="3" width="27.21875" customWidth="1"/>
+    <col min="3" max="3" width="27.28515625" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
         <v>536</v>
       </c>
@@ -64496,8 +64505,11 @@
       <c r="C1" s="17" t="s">
         <v>538</v>
       </c>
+      <c r="D1" t="s">
+        <v>586</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>17</v>
       </c>
@@ -64507,8 +64519,11 @@
       <c r="C2" s="19" t="s">
         <v>577</v>
       </c>
+      <c r="D2" t="s">
+        <v>587</v>
+      </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
         <v>18</v>
       </c>
@@ -64518,8 +64533,11 @@
       <c r="C3" s="19" t="s">
         <v>577</v>
       </c>
+      <c r="D3" t="s">
+        <v>587</v>
+      </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
         <v>19</v>
       </c>
@@ -64529,8 +64547,11 @@
       <c r="C4" s="19" t="s">
         <v>577</v>
       </c>
+      <c r="D4" t="s">
+        <v>587</v>
+      </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>20</v>
       </c>
@@ -64540,8 +64561,11 @@
       <c r="C5" s="19" t="s">
         <v>577</v>
       </c>
+      <c r="D5" t="s">
+        <v>587</v>
+      </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
         <v>21</v>
       </c>
@@ -64551,8 +64575,11 @@
       <c r="C6" s="19" t="s">
         <v>577</v>
       </c>
+      <c r="D6" t="s">
+        <v>587</v>
+      </c>
     </row>
-    <row r="7" spans="1:3" s="11" customFormat="1" ht="25.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" s="11" customFormat="1" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>22</v>
       </c>
@@ -64562,8 +64589,11 @@
       <c r="C7" s="19" t="s">
         <v>577</v>
       </c>
+      <c r="D7" t="s">
+        <v>587</v>
+      </c>
     </row>
-    <row r="8" spans="1:3" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>23</v>
       </c>
@@ -64573,8 +64603,11 @@
       <c r="C8" s="19" t="s">
         <v>577</v>
       </c>
+      <c r="D8" t="s">
+        <v>587</v>
+      </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
         <v>24</v>
       </c>
@@ -64584,8 +64617,11 @@
       <c r="C9" s="19" t="s">
         <v>577</v>
       </c>
+      <c r="D9" t="s">
+        <v>587</v>
+      </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
         <v>25</v>
       </c>
@@ -64595,8 +64631,11 @@
       <c r="C10" s="19" t="s">
         <v>577</v>
       </c>
+      <c r="D10" t="s">
+        <v>587</v>
+      </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
         <v>26</v>
       </c>
@@ -64606,8 +64645,11 @@
       <c r="C11" s="19" t="s">
         <v>577</v>
       </c>
+      <c r="D11" t="s">
+        <v>587</v>
+      </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
         <v>27</v>
       </c>
@@ -64617,8 +64659,11 @@
       <c r="C12" s="19" t="s">
         <v>577</v>
       </c>
+      <c r="D12" t="s">
+        <v>587</v>
+      </c>
     </row>
-    <row r="13" spans="1:3" s="11" customFormat="1" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" s="11" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>28</v>
       </c>
@@ -64628,8 +64673,11 @@
       <c r="C13" s="19" t="s">
         <v>578</v>
       </c>
+      <c r="D13" t="s">
+        <v>587</v>
+      </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
         <v>29</v>
       </c>
@@ -64639,8 +64687,11 @@
       <c r="C14" s="19" t="s">
         <v>578</v>
       </c>
+      <c r="D14" t="s">
+        <v>587</v>
+      </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
         <v>30</v>
       </c>
@@ -64650,8 +64701,11 @@
       <c r="C15" s="19" t="s">
         <v>578</v>
       </c>
+      <c r="D15" t="s">
+        <v>587</v>
+      </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
         <v>31</v>
       </c>
@@ -64661,8 +64715,11 @@
       <c r="C16" s="18" t="s">
         <v>579</v>
       </c>
+      <c r="D16" t="s">
+        <v>587</v>
+      </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
         <v>32</v>
       </c>
@@ -64672,8 +64729,11 @@
       <c r="C17" s="18" t="s">
         <v>579</v>
       </c>
+      <c r="D17" t="s">
+        <v>587</v>
+      </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
         <v>33</v>
       </c>
@@ -64683,8 +64743,11 @@
       <c r="C18" s="18" t="s">
         <v>579</v>
       </c>
+      <c r="D18" t="s">
+        <v>587</v>
+      </c>
     </row>
-    <row r="19" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
         <v>34</v>
       </c>
@@ -64694,8 +64757,11 @@
       <c r="C19" s="19" t="s">
         <v>580</v>
       </c>
+      <c r="D19" t="s">
+        <v>587</v>
+      </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
         <v>35</v>
       </c>
@@ -64705,8 +64771,11 @@
       <c r="C20" s="19" t="s">
         <v>580</v>
       </c>
+      <c r="D20" t="s">
+        <v>587</v>
+      </c>
     </row>
-    <row r="21" spans="1:3" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
         <v>36</v>
       </c>
@@ -64716,8 +64785,11 @@
       <c r="C21" s="19" t="s">
         <v>580</v>
       </c>
+      <c r="D21" t="s">
+        <v>587</v>
+      </c>
     </row>
-    <row r="22" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
         <v>37</v>
       </c>
@@ -64727,8 +64799,11 @@
       <c r="C22" s="18" t="s">
         <v>581</v>
       </c>
+      <c r="D22" t="s">
+        <v>587</v>
+      </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
         <v>38</v>
       </c>
@@ -64738,8 +64813,11 @@
       <c r="C23" s="18" t="s">
         <v>581</v>
       </c>
+      <c r="D23" t="s">
+        <v>587</v>
+      </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="7" t="s">
         <v>39</v>
       </c>
@@ -64749,8 +64827,11 @@
       <c r="C24" s="18" t="s">
         <v>581</v>
       </c>
+      <c r="D24" t="s">
+        <v>587</v>
+      </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
         <v>40</v>
       </c>
@@ -64760,8 +64841,11 @@
       <c r="C25" s="18" t="s">
         <v>582</v>
       </c>
+      <c r="D25" t="s">
+        <v>588</v>
+      </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="8" t="s">
         <v>41</v>
       </c>
@@ -64772,7 +64856,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="8" t="s">
         <v>42</v>
       </c>
@@ -64783,7 +64867,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="8" t="s">
         <v>43</v>
       </c>
@@ -64794,7 +64878,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="8" t="s">
         <v>44</v>
       </c>
@@ -64804,8 +64888,11 @@
       <c r="C29" s="19" t="s">
         <v>583</v>
       </c>
+      <c r="D29" t="s">
+        <v>589</v>
+      </c>
     </row>
-    <row r="30" spans="1:3" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
         <v>45</v>
       </c>
@@ -64815,8 +64902,11 @@
       <c r="C30" s="19" t="s">
         <v>583</v>
       </c>
+      <c r="D30" t="s">
+        <v>589</v>
+      </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
         <v>46</v>
       </c>
@@ -64826,8 +64916,11 @@
       <c r="C31" s="19" t="s">
         <v>583</v>
       </c>
+      <c r="D31" t="s">
+        <v>589</v>
+      </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="8" t="s">
         <v>47</v>
       </c>
@@ -64837,8 +64930,11 @@
       <c r="C32" s="18" t="s">
         <v>584</v>
       </c>
+      <c r="D32" t="s">
+        <v>589</v>
+      </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="8" t="s">
         <v>48</v>
       </c>
@@ -64848,8 +64944,11 @@
       <c r="C33" s="18" t="s">
         <v>584</v>
       </c>
+      <c r="D33" t="s">
+        <v>589</v>
+      </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="8" t="s">
         <v>49</v>
       </c>
@@ -64859,8 +64958,11 @@
       <c r="C34" s="18" t="s">
         <v>584</v>
       </c>
+      <c r="D34" t="s">
+        <v>589</v>
+      </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="8" t="s">
         <v>50</v>
       </c>
@@ -64870,8 +64972,11 @@
       <c r="C35" s="18" t="s">
         <v>584</v>
       </c>
+      <c r="D35" t="s">
+        <v>589</v>
+      </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="6" t="s">
         <v>51</v>
       </c>
@@ -64881,8 +64986,11 @@
       <c r="C36" s="20" t="s">
         <v>585</v>
       </c>
+      <c r="D36" t="s">
+        <v>589</v>
+      </c>
     </row>
-    <row r="37" spans="1:3" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A37" s="8" t="s">
         <v>52</v>
       </c>
@@ -64892,8 +65000,11 @@
       <c r="C37" s="20" t="s">
         <v>585</v>
       </c>
+      <c r="D37" t="s">
+        <v>589</v>
+      </c>
     </row>
-    <row r="38" spans="1:3" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A38" s="8" t="s">
         <v>53</v>
       </c>
@@ -64903,8 +65014,11 @@
       <c r="C38" s="20" t="s">
         <v>585</v>
       </c>
+      <c r="D38" t="s">
+        <v>589</v>
+      </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="21" t="s">
         <v>54</v>
       </c>
@@ -64913,6 +65027,9 @@
       </c>
       <c r="C39" s="20" t="s">
         <v>585</v>
+      </c>
+      <c r="D39" t="s">
+        <v>589</v>
       </c>
     </row>
   </sheetData>

--- a/digi-finance/data/digi-fin-data.xlsx
+++ b/digi-finance/data/digi-fin-data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AER\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AER\Documents\Github repo\data-consultation-2026\digi-finance\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B6B104F-4805-4104-80D9-FE5187CE4250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F809F2F-802D-4981-9C78-3F9590E4F162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Responses" sheetId="1" r:id="rId1"/>
